--- a/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
+++ b/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="65" documentId="8_{73207B45-BDEF-49ED-9CCC-D07D630568B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E09BBE49-4C88-4896-BC7B-7230FC7727B9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -959,10 +959,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1283,10 +1279,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F4B47D-A9BB-48AC-8480-CD7E4C5E1576}">
   <dimension ref="B1:N35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="58" t="s">
         <v>39</v>
       </c>
@@ -1303,7 +1299,7 @@
       <c r="M2" s="59"/>
       <c r="N2" s="60"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="61"/>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -1318,7 +1314,7 @@
       <c r="M3" s="62"/>
       <c r="N3" s="63"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="61"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -1333,7 +1329,7 @@
       <c r="M4" s="62"/>
       <c r="N4" s="63"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="61"/>
       <c r="C5" s="62"/>
       <c r="D5" s="62"/>
@@ -1348,7 +1344,7 @@
       <c r="M5" s="62"/>
       <c r="N5" s="63"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="61"/>
       <c r="C6" s="62"/>
       <c r="D6" s="62"/>
@@ -1363,7 +1359,7 @@
       <c r="M6" s="62"/>
       <c r="N6" s="63"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
@@ -1378,7 +1374,7 @@
       <c r="M7" s="62"/>
       <c r="N7" s="63"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="61"/>
       <c r="C8" s="62"/>
       <c r="D8" s="62"/>
@@ -1393,7 +1389,7 @@
       <c r="M8" s="62"/>
       <c r="N8" s="63"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="61"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
@@ -1408,7 +1404,7 @@
       <c r="M9" s="62"/>
       <c r="N9" s="63"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="61"/>
       <c r="C10" s="62"/>
       <c r="D10" s="62"/>
@@ -1423,7 +1419,7 @@
       <c r="M10" s="62"/>
       <c r="N10" s="63"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="61"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
@@ -1438,7 +1434,7 @@
       <c r="M11" s="62"/>
       <c r="N11" s="63"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="61"/>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
@@ -1453,7 +1449,7 @@
       <c r="M12" s="62"/>
       <c r="N12" s="63"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="61"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
@@ -1468,7 +1464,7 @@
       <c r="M13" s="62"/>
       <c r="N13" s="63"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="61"/>
       <c r="C14" s="62"/>
       <c r="D14" s="62"/>
@@ -1483,7 +1479,7 @@
       <c r="M14" s="62"/>
       <c r="N14" s="63"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="61"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
@@ -1498,7 +1494,7 @@
       <c r="M15" s="62"/>
       <c r="N15" s="63"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="61"/>
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
@@ -1513,7 +1509,7 @@
       <c r="M16" s="62"/>
       <c r="N16" s="63"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="61"/>
       <c r="C17" s="62"/>
       <c r="D17" s="62"/>
@@ -1528,7 +1524,7 @@
       <c r="M17" s="62"/>
       <c r="N17" s="63"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="61"/>
       <c r="C18" s="62"/>
       <c r="D18" s="62"/>
@@ -1543,7 +1539,7 @@
       <c r="M18" s="62"/>
       <c r="N18" s="63"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="61"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
@@ -1558,7 +1554,7 @@
       <c r="M19" s="62"/>
       <c r="N19" s="63"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="61"/>
       <c r="C20" s="62"/>
       <c r="D20" s="62"/>
@@ -1573,7 +1569,7 @@
       <c r="M20" s="62"/>
       <c r="N20" s="63"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="61"/>
       <c r="C21" s="62"/>
       <c r="D21" s="62"/>
@@ -1588,7 +1584,7 @@
       <c r="M21" s="62"/>
       <c r="N21" s="63"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="61"/>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
@@ -1603,7 +1599,7 @@
       <c r="M22" s="62"/>
       <c r="N22" s="63"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="61"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
@@ -1618,7 +1614,7 @@
       <c r="M23" s="62"/>
       <c r="N23" s="63"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="61"/>
       <c r="C24" s="62"/>
       <c r="D24" s="62"/>
@@ -1633,7 +1629,7 @@
       <c r="M24" s="62"/>
       <c r="N24" s="63"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="61"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
@@ -1648,7 +1644,7 @@
       <c r="M25" s="62"/>
       <c r="N25" s="63"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="61"/>
       <c r="C26" s="62"/>
       <c r="D26" s="62"/>
@@ -1663,7 +1659,7 @@
       <c r="M26" s="62"/>
       <c r="N26" s="63"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="61"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
@@ -1678,7 +1674,7 @@
       <c r="M27" s="62"/>
       <c r="N27" s="63"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="61"/>
       <c r="C28" s="62"/>
       <c r="D28" s="62"/>
@@ -1693,7 +1689,7 @@
       <c r="M28" s="62"/>
       <c r="N28" s="63"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="61"/>
       <c r="C29" s="62"/>
       <c r="D29" s="62"/>
@@ -1708,7 +1704,7 @@
       <c r="M29" s="62"/>
       <c r="N29" s="63"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="61"/>
       <c r="C30" s="62"/>
       <c r="D30" s="62"/>
@@ -1723,7 +1719,7 @@
       <c r="M30" s="62"/>
       <c r="N30" s="63"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="61"/>
       <c r="C31" s="62"/>
       <c r="D31" s="62"/>
@@ -1738,7 +1734,7 @@
       <c r="M31" s="62"/>
       <c r="N31" s="63"/>
     </row>
-    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="64"/>
       <c r="C32" s="65"/>
       <c r="D32" s="65"/>
@@ -1753,7 +1749,7 @@
       <c r="M32" s="65"/>
       <c r="N32" s="66"/>
     </row>
-    <row r="35" spans="2:2" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:2" ht="24" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
         <v>41</v>
       </c>
@@ -1769,22 +1765,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEFBDD42-12EA-4BED-9E12-AAFD1F2477F3}">
   <dimension ref="B2:L26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
-    <col min="5" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" customWidth="1"/>
-    <col min="12" max="12" width="14.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:12" ht="24" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" s="67" t="s">
         <v>24</v>
       </c>
@@ -1792,7 +1788,7 @@
       <c r="F3" s="67"/>
       <c r="G3" s="67"/>
     </row>
-    <row r="4" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
@@ -1812,7 +1808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="32.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="27" t="s">
         <v>33</v>
       </c>
@@ -1838,7 +1834,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="35.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:12" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="27" t="s">
         <v>10</v>
       </c>
@@ -1867,7 +1863,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:12" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="27" t="s">
         <v>12</v>
       </c>
@@ -1896,7 +1892,7 @@
         <v>0.21249999999999999</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:12" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="27" t="s">
         <v>13</v>
       </c>
@@ -1926,7 +1922,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:12" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="27" t="s">
         <v>14</v>
       </c>
@@ -1955,7 +1951,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:12" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="29" t="s">
         <v>29</v>
       </c>
@@ -1984,7 +1980,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="31" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J11" s="41" t="s">
         <v>29</v>
       </c>
@@ -1995,7 +1991,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="76" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:12" ht="75.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J12" s="50"/>
       <c r="K12" s="46" t="s">
         <v>31</v>
@@ -2004,12 +2000,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:12" ht="24" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D14" s="67" t="s">
         <v>24</v>
       </c>
@@ -2017,7 +2013,7 @@
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
     </row>
-    <row r="15" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
         <v>3</v>
       </c>
@@ -2037,7 +2033,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>33</v>
       </c>
@@ -2064,7 +2060,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
         <v>10</v>
       </c>
@@ -2091,7 +2087,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
         <v>12</v>
       </c>
@@ -2118,7 +2114,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="29.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
         <v>13</v>
       </c>
@@ -2142,7 +2138,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="44" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
         <v>14</v>
       </c>
@@ -2166,7 +2162,7 @@
         <v>0.46666666666666656</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>30</v>
       </c>
@@ -2190,11 +2186,11 @@
         <v>0.45454545454545464</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
     </row>
-    <row r="23" spans="2:8" ht="37.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:8" ht="57" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="56" t="s">
         <v>34</v>
       </c>
@@ -2216,11 +2212,11 @@
         <v>0.72202949494949487</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D24" s="32"/>
     </row>
-    <row r="25" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="2:8" ht="37.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:8" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="57" t="s">
         <v>35</v>
       </c>
@@ -2273,18 +2269,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B530F8E-8ED6-4B10-8C37-128BAAAF4D41}">
   <dimension ref="B3:N14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D4" s="68" t="s">
         <v>1</v>
       </c>
@@ -2298,7 +2294,7 @@
       <c r="J4" s="69"/>
       <c r="K4" s="69"/>
     </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2333,7 +2329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="32.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" ht="32.450000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2368,7 +2364,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2403,7 +2399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -2438,7 +2434,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
@@ -2473,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
@@ -2508,7 +2504,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:14" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2543,7 +2539,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="D12" s="68" t="s">
         <v>16</v>
       </c>
@@ -2574,7 +2570,7 @@
       </c>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D13" s="68" t="s">
         <v>17</v>
       </c>
@@ -2605,7 +2601,7 @@
       </c>
       <c r="N13" s="42"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D14" s="70" t="s">
         <v>18</v>
       </c>

--- a/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
+++ b/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/btdhd_umsystem_edu/Documents/Desktop/NATR_8001_DecisionAnalysis_Fall25_Mizzou/material/Week5-Tradeoffs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{73207B45-BDEF-49ED-9CCC-D07D630568B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E09BBE49-4C88-4896-BC7B-7230FC7727B9}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{73207B45-BDEF-49ED-9CCC-D07D630568B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2D9A29-B88C-40C0-BE27-0D5927A4CCC3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="43">
   <si>
     <t>Swing Weighting (example)</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Citation: Sarah Converse, Mike Runge, Brielle Thompson</t>
+  </si>
+  <si>
+    <t>Neighbor Satisfaction        (Estimated number)</t>
   </si>
 </sst>
 </file>
@@ -959,6 +962,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1836,7 +1843,7 @@
     </row>
     <row r="6" spans="2:12" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="27" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>9</v>
@@ -2062,26 +2069,26 @@
     </row>
     <row r="17" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="44">
         <f>1-(D6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E17" s="44">
-        <f>1-(E6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
+        <f>(E6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="44">
+        <f>(F6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
+        <v>0.6</v>
+      </c>
+      <c r="G17" s="44">
+        <f>(G6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
         <v>0</v>
-      </c>
-      <c r="F17" s="44">
-        <f>1-(F6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
-        <v>0.4</v>
-      </c>
-      <c r="G17" s="44">
-        <f>1-(G6-MIN($D$6:$G$6))/(MAX($D$6:$G$6)-MIN($D$6:$G$6))</f>
-        <v>1</v>
       </c>
       <c r="H17" s="40" t="s">
         <v>27</v>
@@ -2201,15 +2208,15 @@
       </c>
       <c r="E23" s="48">
         <f t="shared" ref="E23:G23" si="3">SUMPRODUCT(E16:E21,$K$6:$K$11)</f>
-        <v>0.20230000000000001</v>
+        <v>0.36890000000000001</v>
       </c>
       <c r="F23" s="48">
         <f t="shared" si="3"/>
-        <v>0.63783999999999996</v>
+        <v>0.67115999999999998</v>
       </c>
       <c r="G23" s="47">
         <f t="shared" si="3"/>
-        <v>0.72202949494949487</v>
+        <v>0.5554294949494949</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
@@ -2226,15 +2233,15 @@
       </c>
       <c r="E26" s="48">
         <f>SUMPRODUCT(E16:E21,$L$6:$L$11)</f>
-        <v>0.22857142857142856</v>
+        <v>0.44107142857142856</v>
       </c>
       <c r="F26" s="48">
         <f>SUMPRODUCT(F16:F21,$L$6:$L$11)</f>
-        <v>0.55464285714285722</v>
+        <v>0.59714285714285709</v>
       </c>
       <c r="G26" s="47">
         <f>SUMPRODUCT(G16:G21,$L$6:$L$11)</f>
-        <v>0.74676406926406935</v>
+        <v>0.53426406926406922</v>
       </c>
     </row>
   </sheetData>
@@ -2366,37 +2373,37 @@
     </row>
     <row r="7" spans="2:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <v>5</v>
       </c>
-      <c r="E7" s="9">
+      <c r="F7" s="10">
         <v>0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
         <v>5</v>
       </c>
-      <c r="G7" s="11">
-        <v>5</v>
-      </c>
-      <c r="H7" s="12">
+      <c r="I7" s="11">
         <v>0</v>
       </c>
-      <c r="I7" s="11">
-        <v>5</v>
-      </c>
       <c r="J7" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
+++ b/material/Week5-Tradeoffs/Week5-Skillcheck-Completed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/btdhd_umsystem_edu/Documents/Desktop/NATR_8001_DecisionAnalysis_Fall25_Mizzou/material/Week5-Tradeoffs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{73207B45-BDEF-49ED-9CCC-D07D630568B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2D9A29-B88C-40C0-BE27-0D5927A4CCC3}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{73207B45-BDEF-49ED-9CCC-D07D630568B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976A1CF4-84F7-4F6A-B5C1-CF7642FA50E9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8E6094A0-F1BF-4785-B38D-3B1B58DBD82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -962,10 +962,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
